--- a/data/gravel/Mason Macro Al 2025.xlsx
+++ b/data/gravel/Mason Macro Al 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13316C45-D23B-444F-9B23-FE47F7A7BEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9FF131B-3DAF-C644-8AE5-7DFAC3C04801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44080" yWindow="-22100" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -365,9 +365,6 @@
     <t>aluminum</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -387,6 +384,15 @@
   </si>
   <si>
     <t>rear_axle_spec</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>threaded 73</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -1160,7 +1166,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>93</v>
@@ -1418,26 +1424,26 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1466,8 +1472,7 @@
         <v>34</v>
       </c>
       <c r="B47" s="1">
-        <f>2.4*25.4</f>
-        <v>60.959999999999994</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1487,9 +1492,6 @@
       <c r="A50" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
@@ -1505,16 +1507,25 @@
       <c r="A53" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="B53" s="1">
+        <v>148</v>
+      </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="B54" s="1">
+        <v>110</v>
+      </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="B55" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
@@ -1530,6 +1541,9 @@
       <c r="A58" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="B58" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
@@ -1545,16 +1559,25 @@
       <c r="A61" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="B61" s="1">
+        <v>180</v>
+      </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="B62" s="1">
+        <v>180</v>
+      </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B63" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
@@ -1568,11 +1591,17 @@
       <c r="A65" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B65" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="B66" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
@@ -1583,36 +1612,57 @@
       <c r="A68" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="B68" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="B69" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="B70" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="B71" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="B72" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="B73" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
         <v>61</v>
       </c>
+      <c r="B74" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
@@ -1634,16 +1684,13 @@
       <c r="A77" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Mason Macro Al 2025.xlsx
+++ b/data/gravel/Mason Macro Al 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9FF131B-3DAF-C644-8AE5-7DFAC3C04801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342A92E3-2552-464F-B415-2BC8FC3AF3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44080" yWindow="-22100" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="500" windowWidth="24660" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -393,6 +393,12 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>https://masoncycles.cc/images/000/009/464/large/Macro_TS_Side_Rack_Web.jpg?1742486567</t>
   </si>
 </sst>
 </file>
@@ -793,6 +799,14 @@
         <v>104</v>
       </c>
     </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
         <v>5</v>
@@ -1491,6 +1505,9 @@
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="B50" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2">

--- a/data/gravel/Mason Macro Al 2025.xlsx
+++ b/data/gravel/Mason Macro Al 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342A92E3-2552-464F-B415-2BC8FC3AF3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258C81AB-0F8C-A649-9AB9-BD861A0D6D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="500" windowWidth="24660" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4140" yWindow="500" windowWidth="24660" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/gravel/Mason Macro Al 2025.xlsx
+++ b/data/gravel/Mason Macro Al 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258C81AB-0F8C-A649-9AB9-BD861A0D6D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1AABBC-C8A9-5347-AA20-075EF8CB375E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="500" windowWidth="24660" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14300" yWindow="780" windowWidth="24660" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1553,6 +1553,9 @@
       <c r="A57" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="B57" s="1">
+        <v>31.6</v>
+      </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
@@ -1565,6 +1568,9 @@
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="B59" s="1">
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:2">

--- a/data/gravel/Mason Macro Al 2025.xlsx
+++ b/data/gravel/Mason Macro Al 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1AABBC-C8A9-5347-AA20-075EF8CB375E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7AC88B-B7A4-5747-97B3-DE07AA03FCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14300" yWindow="780" windowWidth="24660" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4140" yWindow="780" windowWidth="24660" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -399,6 +399,12 @@
   </si>
   <si>
     <t>https://masoncycles.cc/images/000/009/464/large/Macro_TS_Side_Rack_Web.jpg?1742486567</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Lancing, West Sussex, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -751,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1716,6 +1722,14 @@
         <v>117</v>
       </c>
     </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
